--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92563388206</v>
+        <v>46157.93075347799</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93075347799</v>
+        <v>46157.93158669109</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93158669109</v>
+        <v>46157.93395082055</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93395082055</v>
+        <v>46157.93711763153</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93711763153</v>
+        <v>46158.28211946534</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28211946534</v>
+        <v>46158.29672950556</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29672950556</v>
+        <v>46158.29808010479</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29808010479</v>
+        <v>46158.33382737762</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33382737762</v>
+        <v>46158.368503994</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/14. ИП Черевач Денис (перевозка 009)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.368503994</v>
+        <v>46158.37282857863</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
